--- a/QCM1_2_PHY.xlsx
+++ b/QCM1_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FE25E7-E608-400B-BE32-39A480A1F955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AF4DAB-4F37-41FE-8171-B7D062692216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,9 +141,6 @@
     <t>$0,85\text{ m}$</t>
   </si>
   <si>
-    <t>$T = 2,5\text{ \mu s}$</t>
-  </si>
-  <si>
     <t>$T = 25\text{ ms}$</t>
   </si>
   <si>
@@ -456,9 +453,6 @@
     <t>Une onde progressive s'accompagne :</t>
   </si>
   <si>
-    <t>Une onde sonore se propage dans l'air à $340\text{ m.s}^{-1}$. Parmi les affirmations reprises ci-dessous quelle est celle qui est correcte ?</t>
-  </si>
-  <si>
     <t>Sur la figure suivante, vous pouvez voir une impulsion se propageant vers la droite à une vitesse v dans une corde. Le point P est un point de la corde. Parmi les vecteurs suivants, lequel donne la direction et le sens dans lequel le point P se déplace à cet instant ?</t>
   </si>
   <si>
@@ -526,23 +520,12 @@
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Ondes :&lt;/b&gt;&lt;/center&gt;</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_1_Q1.png; PHY_QCM1_1_Q2.png</t>
   </si>
   <si>
     <t>Une onde ultrasonore de fréquence $f = 40\text{ kHz}$ se propage à la célérité $c = 340\text{ m.s}^{-1}$.
 &lt;br&gt;Sa longueur d'onde vaut :</t>
   </si>
   <si>
-    <t>Un homme émet un cri en direction d'une montagne qui se trouve à une distance D. Le temps mesuré entre l'émission du cri et la réception de son écho est $\Delta t = 4\text{ s}$.
-&lt;b&gt;La distance D entre l'homme et la montagne sachant que la vitesse du son dans l'air est $v_s = 330\text{ m.s}^{-1}$ :</t>
-  </si>
-  <si>
-    <t>Une onde se propage avec une célérité $200\text{ m.s}^{-1}$ entre deux points A et B. Elle atteint B, $0,20\text{ s}$ après avoir atteint le point A.
-&lt;b&gt;Quelle distance sépare A et B ?</t>
-  </si>
-  <si>
     <t>&lt;center&gt;&lt;b&gt;Une corde élastique :&lt;/b&gt;&lt;/center&gt;
  Sur une corde élastique se propage une onde mécanique progressive sinusoïdale. A un instant $t_1$ l'allongement d'un point M de la corde est maximal et à un instant $t_2$ il devient nul. On donne $\Delta t = t_2 - t_1 = 0,15\text{ s}$.</t>
   </si>
@@ -561,9 +544,6 @@
 La vitesse des ultrasons dans l'air est de $v_{air} = 300\text{ m.s}^{-1}$. Cette vitesse est plus faible que la vitesse $v_{eau}$ des ultrasons dans l'eau. Un émetteur produit des salves ultrasonores qui se propagent simultanément dans l'air et dans l'eau. 2 récepteurs A et B sont placés à une distance $d = 1,5\text{ m}$ de l'émetteur. Les 2 voies d'un oscilloscope sont reliées aux récepteurs A et B.</t>
   </si>
   <si>
-    <t>PHY_QCM1_1_Q5.png; PHY_QCM1_1_Q6.png</t>
-  </si>
-  <si>
     <t>&lt;center&gt;&lt;b&gt;Un sonar : &lt;/b&gt;&lt;/center&gt;
 L'équipage d'un bateau désire connaître le relief sous-marin à l'aide d'un sonar. Le bateau se déplace suivant un axe (Ox). A intervalle régulier, le sonar envoie une salve d'ondes ultrasonores et enregistre le décalage $\Delta t$ entre le signal émis et l'écho. $P$ désigne la profondeur.</t>
   </si>
@@ -587,9 +567,6 @@
     <t>PHY_QCM1_1_Q7.png</t>
   </si>
   <si>
-    <t>PHY_QCM1_1_Q8.png; PHY_QCM1_1_Q9.png</t>
-  </si>
-  <si>
     <t>PHY_QCM1_1_Q10.png</t>
   </si>
   <si>
@@ -621,6 +598,30 @@
   </si>
   <si>
     <t>$\lambda = 40\text{ cm}$</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_1_Q1_2</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_1_Q5_6.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_1_Q8_9.png</t>
+  </si>
+  <si>
+    <t>$T = 2,5  \mu s$</t>
+  </si>
+  <si>
+    <t>Une onde se propage avec une célérité $200\text{ m.s}^{-1}$ entre deux points A et B. Elle atteint B, $0,20\text{ s}$ après avoir atteint le point A.
+&lt;br&gt;Quelle distance sépare A et B ?</t>
+  </si>
+  <si>
+    <t>Un homme émet un cri en direction d'une montagne qui se trouve à une distance D. Le temps mesuré entre l'émission du cri et la réception de son écho est $\Delta t = 4\text{ s}$.
+&lt;br&gt;La distance D entre l'homme et la montagne sachant que la vitesse du son dans l'air est $v_s = 330\text{ m.s}^{-1}$ :</t>
+  </si>
+  <si>
+    <t>Une onde sonore se propage dans l'air à $340\text{ m.s}^{-1}$. 
+&lt;br&gt;Parmi les affirmations reprises ci-dessous quelle est celle qui est correcte ?</t>
   </si>
 </sst>
 </file>
@@ -1148,10 +1149,10 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>3</v>
@@ -1169,7 +1170,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>14</v>
@@ -1179,7 +1180,7 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>3</v>
@@ -1197,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>21</v>
@@ -1208,7 +1209,7 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>3</v>
@@ -1226,7 +1227,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>20</v>
@@ -1237,7 +1238,7 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
@@ -1255,7 +1256,7 @@
         <v>25</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>23</v>
@@ -1266,7 +1267,7 @@
     <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="7" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
@@ -1295,7 +1296,7 @@
     <row r="7" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>3</v>
@@ -1319,14 +1320,14 @@
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>3</v>
@@ -1344,7 +1345,7 @@
         <v>37</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>36</v>
@@ -1355,28 +1356,28 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="H9" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1384,28 +1385,28 @@
     <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="9" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="H10" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1413,121 +1414,121 @@
     <row r="11" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="9" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="H11" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>53</v>
-      </c>
       <c r="H12" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1535,518 +1536,518 @@
     <row r="15" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="K15" s="5"/>
     </row>
     <row r="16" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>68</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>13</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J17" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>72</v>
-      </c>
       <c r="H18" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="G19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="H19" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>80</v>
-      </c>
       <c r="H20" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="G21" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>84</v>
-      </c>
       <c r="H21" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="G22" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="9" t="s">
-        <v>88</v>
-      </c>
       <c r="H22" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="G23" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="H23" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="J24" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>97</v>
-      </c>
       <c r="H25" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="F26" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="G26" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="H26" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="G27" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="G27" s="9" t="s">
-        <v>105</v>
-      </c>
       <c r="H27" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="F28" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="G28" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="G28" s="9" t="s">
-        <v>109</v>
-      </c>
       <c r="H28" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J28" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="G29" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>113</v>
-      </c>
       <c r="H29" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="F30" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="G30" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="H30" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="G31" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
       <c r="B32" s="9" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="F32" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="G32" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G32" s="9" t="s">
-        <v>122</v>
-      </c>
       <c r="H32" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/QCM1_2_PHY.xlsx
+++ b/QCM1_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AF4DAB-4F37-41FE-8171-B7D062692216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAE5AF7-A5C7-4BE4-B881-4E517B7D2235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,9 +144,6 @@
     <t>$T = 25\text{ ms}$</t>
   </si>
   <si>
-    <t>$T = 25\text{ \mu s}$</t>
-  </si>
-  <si>
     <t>$T = 2,5\text{ ms}$</t>
   </si>
   <si>
@@ -600,16 +597,10 @@
     <t>$\lambda = 40\text{ cm}$</t>
   </si>
   <si>
-    <t>PHY_QCM1_1_Q1_2</t>
-  </si>
-  <si>
     <t>PHY_QCM1_1_Q5_6.png</t>
   </si>
   <si>
     <t>PHY_QCM1_1_Q8_9.png</t>
-  </si>
-  <si>
-    <t>$T = 2,5  \mu s$</t>
   </si>
   <si>
     <t>Une onde se propage avec une célérité $200\text{ m.s}^{-1}$ entre deux points A et B. Elle atteint B, $0,20\text{ s}$ après avoir atteint le point A.
@@ -622,6 +613,15 @@
   <si>
     <t>Une onde sonore se propage dans l'air à $340\text{ m.s}^{-1}$. 
 &lt;br&gt;Parmi les affirmations reprises ci-dessous quelle est celle qui est correcte ?</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_1_Q1_2.png</t>
+  </si>
+  <si>
+    <t>$T = 2,5 \, \mu\mathrm{s}$</t>
+  </si>
+  <si>
+    <t>$T = 25 \, \mu\mathrm{s}$</t>
   </si>
 </sst>
 </file>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>3</v>
@@ -1170,7 +1170,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>14</v>
@@ -1180,7 +1180,7 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>3</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>21</v>
@@ -1209,7 +1209,7 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>3</v>
@@ -1227,7 +1227,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>20</v>
@@ -1238,7 +1238,7 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>25</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>23</v>
@@ -1267,7 +1267,7 @@
     <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
@@ -1296,7 +1296,7 @@
     <row r="7" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>3</v>
@@ -1320,14 +1320,14 @@
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>3</v>
@@ -1345,7 +1345,7 @@
         <v>37</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>36</v>
@@ -1356,25 +1356,25 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="H9" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>38</v>
@@ -1385,28 +1385,28 @@
     <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>44</v>
-      </c>
       <c r="H10" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1414,121 +1414,121 @@
     <row r="11" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>48</v>
-      </c>
       <c r="H11" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>52</v>
-      </c>
       <c r="H12" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1536,518 +1536,518 @@
     <row r="15" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K15" s="5"/>
     </row>
     <row r="16" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>184</v>
-      </c>
       <c r="I16" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>67</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>13</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="H18" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="G19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="H19" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="H20" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="G21" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>83</v>
-      </c>
       <c r="H21" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="G22" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="9" t="s">
-        <v>87</v>
-      </c>
       <c r="H22" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="G23" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="H23" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="G24" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>96</v>
-      </c>
       <c r="H25" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="F26" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="G26" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>100</v>
-      </c>
       <c r="H26" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="G27" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G27" s="9" t="s">
-        <v>104</v>
-      </c>
       <c r="H27" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="F28" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="G28" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="G28" s="9" t="s">
-        <v>108</v>
-      </c>
       <c r="H28" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="G29" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="H29" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="F30" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="G30" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="H30" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="G31" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
       <c r="B32" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="F32" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="G32" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="9" t="s">
-        <v>121</v>
-      </c>
       <c r="H32" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/QCM1_2_PHY.xlsx
+++ b/QCM1_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAE5AF7-A5C7-4BE4-B881-4E517B7D2235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7434B3CC-8F04-4C04-B4FA-8DE77BAB5886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -618,10 +618,10 @@
     <t>PHY_QCM1_1_Q1_2.png</t>
   </si>
   <si>
-    <t>$T = 2,5 \, \mu\mathrm{s}$</t>
-  </si>
-  <si>
     <t>$T = 25 \, \mu\mathrm{s}$</t>
+  </si>
+  <si>
+    <t>$T = 2,5 \, \mu\text{s}$</t>
   </si>
 </sst>
 </file>
@@ -1362,13 +1362,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>39</v>

--- a/QCM1_2_PHY.xlsx
+++ b/QCM1_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7434B3CC-8F04-4C04-B4FA-8DE77BAB5886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B708149-B2A3-40E6-8848-5F28AB5A21DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -553,10 +553,6 @@
 Un vibreur électrique de fréquence $N = 50\text{ Hz}$ crée une onde mécanique progressive. La figure représente l'aspect de la surface.</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Ondes et médecine : &lt;/b&gt;&lt;/center&gt;
-En médecine on utilise différents types de lasers en fonction des effets recherchés. Un laser type $CO_2$ ($10,6\text{ \mu m}$) est utilisé en chirurgie, un laser type Argon Ar ($0,488\text{ \mu m}$) est utilisé en ophtalmologie. $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
-  </si>
-  <si>
     <t>&lt;center&gt;&lt;b&gt;Cuve à ondes : &lt;/b&gt;&lt;/center&gt;
 Sur une cuve à onde, on fait tomber des gouttes d'eau à intervalles de temps réguliers à la fréquence de 120 gouttes par minute. La profondeur de la cuve est constante. On obtient par stroboscopie la figure suivante. La distance $d$ mesure $6\text{ cm}$.</t>
   </si>
@@ -622,6 +618,10 @@
   </si>
   <si>
     <t>$T = 2,5 \, \mu\text{s}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Ondes et médecine : &lt;/b&gt;&lt;/center&gt;
+En médecine on utilise différents types de lasers en fonction des effets recherchés. Un laser type $CO_2$ ($10,6 \, \mu\mathrm{m}$) est utilisé en chirurgie, un laser type Argon Ar ($0,488 \, \mu\text{m}$) est utilisé en ophtalmologie. $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1267,7 @@
     <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
@@ -1320,7 +1320,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K7" s="5"/>
     </row>
@@ -1362,13 +1362,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>39</v>
@@ -1385,7 +1385,7 @@
     <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>3</v>
@@ -1414,7 +1414,7 @@
     <row r="11" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>3</v>
@@ -1548,7 +1548,7 @@
         <v>61</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>62</v>
@@ -1557,7 +1557,7 @@
         <v>12</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>168</v>
@@ -1573,22 +1573,22 @@
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>183</v>
-      </c>
       <c r="I16" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -1622,7 +1622,7 @@
         <v>64</v>
       </c>
       <c r="J17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1762,7 +1762,7 @@
         <v>84</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1792,7 +1792,7 @@
         <v>88</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="51" x14ac:dyDescent="0.25">
@@ -1806,13 +1806,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>91</v>
@@ -1821,10 +1821,10 @@
         <v>133</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1883,7 +1883,7 @@
     </row>
     <row r="27" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>158</v>
@@ -1912,7 +1912,7 @@
     </row>
     <row r="28" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>159</v>
@@ -1939,7 +1939,7 @@
         <v>104</v>
       </c>
       <c r="J28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">

--- a/QCM1_2_PHY.xlsx
+++ b/QCM1_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B708149-B2A3-40E6-8848-5F28AB5A21DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBA0AD4-198D-4A3B-9B28-AFC3F65EA015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -519,10 +519,6 @@
     <t>&lt;center&gt;&lt;b&gt;Ondes :&lt;/b&gt;&lt;/center&gt;</t>
   </si>
   <si>
-    <t>Une onde ultrasonore de fréquence $f = 40\text{ kHz}$ se propage à la célérité $c = 340\text{ m.s}^{-1}$.
-&lt;br&gt;Sa longueur d'onde vaut :</t>
-  </si>
-  <si>
     <t>&lt;center&gt;&lt;b&gt;Une corde élastique :&lt;/b&gt;&lt;/center&gt;
  Sur une corde élastique se propage une onde mécanique progressive sinusoïdale. A un instant $t_1$ l'allongement d'un point M de la corde est maximal et à un instant $t_2$ il devient nul. On donne $\Delta t = t_2 - t_1 = 0,15\text{ s}$.</t>
   </si>
@@ -622,6 +618,10 @@
   <si>
     <t>&lt;center&gt;&lt;b&gt;Ondes et médecine : &lt;/b&gt;&lt;/center&gt;
 En médecine on utilise différents types de lasers en fonction des effets recherchés. Un laser type $CO_2$ ($10,6 \, \mu\mathrm{m}$) est utilisé en chirurgie, un laser type Argon Ar ($0,488 \, \mu\text{m}$) est utilisé en ophtalmologie. $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
+  </si>
+  <si>
+    <t>Une onde ultrasonore de fréquence $f = 40\text{ Hz}$ se propage à la célérité $c = 340\text{ m.s}^{-1}$.
+&lt;br&gt;Sa longueur d'onde vaut :</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1267,7 @@
     <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
@@ -1320,14 +1320,14 @@
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="9" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>3</v>
@@ -1362,13 +1362,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>39</v>
@@ -1385,7 +1385,7 @@
     <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>3</v>
@@ -1414,7 +1414,7 @@
     <row r="11" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>3</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="12" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>143</v>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="13" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>144</v>
@@ -1500,7 +1500,7 @@
         <v>52</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K13" s="5"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>61</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>62</v>
@@ -1557,10 +1557,10 @@
         <v>12</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K15" s="5"/>
     </row>
@@ -1573,29 +1573,29 @@
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>182</v>
-      </c>
       <c r="I16" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>148</v>
@@ -1622,7 +1622,7 @@
         <v>64</v>
       </c>
       <c r="J17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="22" spans="1:10" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>153</v>
@@ -1762,7 +1762,7 @@
         <v>84</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1792,12 +1792,12 @@
         <v>88</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>155</v>
@@ -1806,13 +1806,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>91</v>
@@ -1821,10 +1821,10 @@
         <v>133</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1883,7 +1883,7 @@
     </row>
     <row r="27" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>158</v>
@@ -1912,7 +1912,7 @@
     </row>
     <row r="28" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>159</v>
@@ -1939,7 +1939,7 @@
         <v>104</v>
       </c>
       <c r="J28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2026,7 +2026,7 @@
     <row r="32" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
       <c r="B32" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>3</v>
